--- a/25-06-26/Salman.xlsx
+++ b/25-06-26/Salman.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D20F7C-46AE-46FA-9B1D-336C37DBEE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261BBDA0-156F-4423-A363-3608876DD873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="121">
   <si>
     <t>Gm</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>Address: Walton Road</t>
+  </si>
+  <si>
+    <t>Shop off</t>
   </si>
 </sst>
 </file>
@@ -3378,7 +3381,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3406,7 +3409,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4605,7 +4608,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4633,7 +4636,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5826,7 +5829,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5854,7 +5857,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7047,7 +7050,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7075,7 +7078,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8268,7 +8271,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8296,7 +8299,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9489,7 +9492,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9517,7 +9520,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10707,7 +10710,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10735,7 +10738,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11924,7 +11927,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11952,7 +11955,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13141,7 +13144,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13169,7 +13172,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14358,7 +14361,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14386,7 +14389,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18325,7 +18328,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18353,7 +18356,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19542,7 +19545,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19570,7 +19573,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20759,7 +20762,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20787,7 +20790,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21976,7 +21979,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22004,7 +22007,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23198,7 +23201,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23226,7 +23229,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23437,7 +23440,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23523,11 +23526,11 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2885.4375</v>
+        <v>2098.5</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23539,23 +23542,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>230.83499999999998</v>
+        <v>167.88</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>2654.6025</v>
+        <v>1930.62</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>595.55430000000001</v>
+        <v>436.27815000000004</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>57.700355999999999</v>
+        <v>35.618889750000001</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>3307.8571559999996</v>
+        <v>2402.5170397500001</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23597,15 +23600,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>2360.8125</v>
+        <v>2098.5</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23613,23 +23616,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>188.86500000000001</v>
+        <v>167.88</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>2171.9475000000002</v>
+        <v>1930.62</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>535.5372000000001</v>
+        <v>459.36165000000005</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>43.6718835</v>
+        <v>35.734307250000001</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>2751.1565835000006</v>
+        <v>2425.7159572499995</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23741,11 +23744,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>2832.96</v>
+        <v>2469.7600000000002</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -23757,23 +23760,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>226.63679999999999</v>
+        <v>197.58080000000001</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>2606.3231999999998</v>
+        <v>2272.1792</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>605.35270400000002</v>
+        <v>531.84102399999995</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>16.058379519999999</v>
+        <v>14.02010112</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>3227.7342835199997</v>
+        <v>2818.04032512</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23781,7 +23784,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>1230.7807425000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23811,15 +23814,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>1307.52</v>
+        <v>944.32</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23827,23 +23830,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>104.6016</v>
+        <v>75.545600000000007</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>1202.9184</v>
+        <v>868.77440000000001</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>296.60364800000002</v>
+        <v>207.11116799999999</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>7.4976102400000002</v>
+        <v>5.37942784</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>1507.0196582400001</v>
+        <v>1081.26499584</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23881,11 +23884,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>3849.92</v>
+        <v>3123.52</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -23897,23 +23900,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>307.99360000000001</v>
+        <v>249.88160000000002</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>3541.9264000000003</v>
+        <v>2873.6383999999998</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>728.14336000000003</v>
+        <v>581.12</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>31.134085120000002</v>
+        <v>27.057528320000003</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>4301.2038451200006</v>
+        <v>3481.8159283199998</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -24141,7 +24144,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24152,15 +24155,15 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>16767.349999999999</v>
+        <v>14265.300000000001</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
@@ -24168,23 +24171,23 @@
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1235.4670000000001</v>
+        <v>1035.3030000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>15408.308500000001</v>
+        <v>13106.422500000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>3414.488402</v>
+        <v>2869.0091819999998</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>175.48175283</v>
+        <v>137.22969273000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>18998.278654830003</v>
+        <v>16112.66137473</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24314,7 +24317,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>18998.278654829999</v>
+        <v>16112.66137473</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24347,7 +24350,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>16767.349999999999</v>
+        <v>14265.300000000001</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24368,7 +24371,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>1235.4670000000001</v>
+        <v>1035.3030000000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24411,7 +24414,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>15408.308499999997</v>
+        <v>13106.422500000001</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24436,7 +24439,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>3414.488402</v>
+        <v>2869.0091819999998</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24458,7 +24461,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>18822.796901999998</v>
+        <v>15975.431682</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24483,7 +24486,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>470.56992255</v>
+        <v>399.38579205000002</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24493,7 +24496,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>19293.366824549998</v>
+        <v>16374.81747405</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24594,7 +24597,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD37"/>
+  <dimension ref="A1:XFD37"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
@@ -24616,6 +24619,11 @@
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+    </row>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="199" t="s">
         <v>45</v>
@@ -24665,7 +24673,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24693,7 +24701,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25163,12 +25171,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>5</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="3"/>
-        <v>363.2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -25177,23 +25183,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="5"/>
-        <v>29.056000000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="6"/>
-        <v>334.14400000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>73.511679999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="1"/>
-        <v>2.0382784000000003</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="2"/>
-        <v>409.69395840000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25221,39 +25227,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>5</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="3"/>
-        <v>363.2</v>
-      </c>
-      <c r="J20" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="5"/>
-        <v>29.056000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="6"/>
-        <v>334.14400000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>89.49248</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="1"/>
-        <v>2.1181824000000002</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="2"/>
-        <v>425.75466240000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25281,12 +25283,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>10</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="3"/>
-        <v>726.4</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -25295,23 +25295,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="5"/>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="6"/>
-        <v>668.28800000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>147.02336</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="1"/>
-        <v>4.0765568000000005</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="2"/>
-        <v>819.38791680000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25497,11 +25497,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1452.8</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -25510,23 +25510,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25576,7 +25576,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1452.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25597,7 +25597,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>116.224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25640,7 +25640,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25687,7 +25687,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1646.6035200000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25722,7 +25722,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25894,7 +25894,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25922,7 +25922,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27125,7 +27125,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27153,7 +27153,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28353,7 +28353,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28381,7 +28381,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29578,7 +29578,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29606,7 +29606,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30817,7 +30817,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30845,7 +30845,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31139,12 +31139,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>15</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>786.9375</v>
+        <v>0</v>
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
@@ -31153,23 +31151,23 @@
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>62.954999999999998</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>723.98249999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>159.27615</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>22.081466250000002</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>905.34011624999994</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -31201,39 +31199,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>5</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>262.3125</v>
-      </c>
-      <c r="J17" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>20.984999999999999</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>241.32749999999999</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>76.175550000000001</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>7.9375762499999993</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>325.44062624999998</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -31647,11 +31641,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1049.25</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -31660,23 +31654,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>83.94</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>965.31</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>235.45170000000002</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>30.019042500000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1230.7807424999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31726,7 +31720,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1049.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31747,7 +31741,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>83.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31790,7 +31784,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>965.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31815,7 +31809,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>235.45170000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31837,7 +31831,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1200.7617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31862,7 +31856,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>30.019042500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31872,7 +31866,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1230.7807425000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
